--- a/tests/fixtures/05_expense_report/05_expense_report_pattern-from-claude.xlsx
+++ b/tests/fixtures/05_expense_report/05_expense_report_pattern-from-claude.xlsx
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>\d+(\.\d+)?</t>
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
